--- a/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487768_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487768_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>A. DIAZ FERREIRA</t>
+          <t>T. PIERRE PHILIPPE</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.4939</v>
+        <v>5.2172</v>
       </c>
       <c r="E2" t="n">
-        <v>2.6734</v>
+        <v>4.8612</v>
       </c>
       <c r="F2" t="n">
-        <v>1.8205</v>
+        <v>0.356</v>
       </c>
       <c r="G2" t="n">
-        <v>3.7504</v>
+        <v>5.6277</v>
       </c>
       <c r="H2" t="n">
-        <v>2.1535</v>
+        <v>0.1299</v>
       </c>
       <c r="I2" t="n">
-        <v>1.5969</v>
+        <v>5.4978</v>
       </c>
       <c r="J2" t="n">
-        <v>1.7666</v>
+        <v>4.9258</v>
       </c>
       <c r="K2" t="n">
-        <v>1.4923</v>
+        <v>0.2894</v>
       </c>
       <c r="L2" t="n">
-        <v>0.2743</v>
+        <v>4.6364</v>
       </c>
       <c r="M2" t="n">
-        <v>1.9838</v>
+        <v>0.7019</v>
       </c>
       <c r="N2" t="n">
-        <v>0.6612</v>
+        <v>-0.1595</v>
       </c>
       <c r="O2" t="n">
-        <v>1.3226</v>
+        <v>0.8613</v>
       </c>
       <c r="P2" t="n">
-        <v>0.8325</v>
+        <v>-1.2487</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>-2.0812</v>
       </c>
       <c r="R2" t="n">
         <v>0.8325</v>
       </c>
       <c r="S2" t="n">
-        <v>1.5384</v>
+        <v>-0.0993</v>
       </c>
       <c r="T2" t="n">
-        <v>0.9068000000000001</v>
+        <v>0.2653</v>
       </c>
       <c r="U2" t="n">
-        <v>0.6316000000000001</v>
+        <v>-0.3646</v>
       </c>
       <c r="V2" t="n">
-        <v>-1.6275</v>
+        <v>0.9376</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>1.7513</v>
       </c>
       <c r="X2" t="n">
-        <v>-1.6275</v>
+        <v>-0.8137</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>T. PIERRE PHILIPPE</t>
+          <t>G. ARCOS GONZALEZ</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.4717</v>
+        <v>4.2561</v>
       </c>
       <c r="E3" t="n">
-        <v>4.4093</v>
+        <v>2.3354</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0624</v>
+        <v>1.9207</v>
       </c>
       <c r="G3" t="n">
-        <v>5.6277</v>
+        <v>3.2881</v>
       </c>
       <c r="H3" t="n">
-        <v>0.1299</v>
+        <v>1.674</v>
       </c>
       <c r="I3" t="n">
-        <v>5.4978</v>
+        <v>1.6141</v>
       </c>
       <c r="J3" t="n">
-        <v>4.9258</v>
+        <v>2.472</v>
       </c>
       <c r="K3" t="n">
-        <v>0.2894</v>
+        <v>1.6458</v>
       </c>
       <c r="L3" t="n">
-        <v>4.6364</v>
+        <v>0.8262</v>
       </c>
       <c r="M3" t="n">
-        <v>0.7019</v>
+        <v>0.8161</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.1595</v>
+        <v>0.0283</v>
       </c>
       <c r="O3" t="n">
-        <v>0.8613</v>
+        <v>0.7879</v>
       </c>
       <c r="P3" t="n">
-        <v>-1.2487</v>
+        <v>1.4568</v>
       </c>
       <c r="Q3" t="n">
-        <v>-2.0812</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>0.8325</v>
+        <v>1.4568</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.8449</v>
+        <v>-0.135</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.1866</v>
+        <v>0.2172</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.6582</v>
+        <v>-0.3522</v>
       </c>
       <c r="V3" t="n">
-        <v>0.9376</v>
+        <v>-0.3538</v>
       </c>
       <c r="W3" t="n">
-        <v>1.7513</v>
+        <v>-0.3538</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.8137</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>J. MENENDEZ GARCIA</t>
+          <t>A. DIAZ FERREIRA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.2432</v>
+        <v>3.8331</v>
       </c>
       <c r="E4" t="n">
-        <v>1.1408</v>
+        <v>2.4824</v>
       </c>
       <c r="F4" t="n">
-        <v>2.1024</v>
+        <v>1.3507</v>
       </c>
       <c r="G4" t="n">
-        <v>3.0974</v>
+        <v>3.7504</v>
       </c>
       <c r="H4" t="n">
-        <v>1.876</v>
+        <v>2.1535</v>
       </c>
       <c r="I4" t="n">
-        <v>1.2214</v>
+        <v>1.5969</v>
       </c>
       <c r="J4" t="n">
-        <v>1.8527</v>
+        <v>1.7666</v>
       </c>
       <c r="K4" t="n">
-        <v>1.7049</v>
+        <v>1.4923</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1478</v>
+        <v>0.2743</v>
       </c>
       <c r="M4" t="n">
-        <v>1.2448</v>
+        <v>1.9838</v>
       </c>
       <c r="N4" t="n">
-        <v>0.1711</v>
+        <v>0.6612</v>
       </c>
       <c r="O4" t="n">
-        <v>1.0736</v>
+        <v>1.3226</v>
       </c>
       <c r="P4" t="n">
-        <v>-2.7055</v>
+        <v>0.8325</v>
       </c>
       <c r="Q4" t="n">
-        <v>-4.1624</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.4568</v>
+        <v>0.8325</v>
       </c>
       <c r="S4" t="n">
-        <v>4.0188</v>
+        <v>0.8777</v>
       </c>
       <c r="T4" t="n">
-        <v>3.4505</v>
+        <v>0.7158</v>
       </c>
       <c r="U4" t="n">
-        <v>0.5684</v>
+        <v>0.1619</v>
       </c>
       <c r="V4" t="n">
-        <v>-1.1675</v>
+        <v>-1.6275</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.1675</v>
+        <v>-1.6275</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>J. LUIS</t>
+          <t>D. RAMÍREZ SÁNCHEZ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.9552</v>
+        <v>1.8091</v>
       </c>
       <c r="E5" t="n">
-        <v>3.1415</v>
+        <v>0.2429</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.1863</v>
+        <v>1.5661</v>
       </c>
       <c r="G5" t="n">
-        <v>1.2524</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.6654</v>
+        <v>0.5482</v>
       </c>
       <c r="I5" t="n">
-        <v>1.9178</v>
+        <v>0.3919</v>
       </c>
       <c r="J5" t="n">
-        <v>2.6324</v>
+        <v>0.8177</v>
       </c>
       <c r="K5" t="n">
-        <v>0.6820000000000001</v>
+        <v>0.7483</v>
       </c>
       <c r="L5" t="n">
-        <v>1.9504</v>
+        <v>0.0694</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.38</v>
+        <v>0.1223</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.3473</v>
+        <v>-0.2002</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.0326</v>
+        <v>0.3225</v>
       </c>
       <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
         <v>-1.0406</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>-2.0812</v>
       </c>
       <c r="R5" t="n">
         <v>1.0406</v>
       </c>
       <c r="S5" t="n">
-        <v>3.2033</v>
+        <v>0.869</v>
       </c>
       <c r="T5" t="n">
-        <v>2.3603</v>
+        <v>0.4658</v>
       </c>
       <c r="U5" t="n">
-        <v>0.843</v>
+        <v>0.4032</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.4599</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>0.23</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.6899</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>G. ARCOS GONZALEZ</t>
+          <t>J. MENENDEZ GARCIA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>2.8573</v>
+        <v>0.9919</v>
       </c>
       <c r="E6" t="n">
-        <v>1.3476</v>
+        <v>-0.6995</v>
       </c>
       <c r="F6" t="n">
-        <v>1.5097</v>
+        <v>1.6914</v>
       </c>
       <c r="G6" t="n">
-        <v>3.2881</v>
+        <v>3.0974</v>
       </c>
       <c r="H6" t="n">
-        <v>1.674</v>
+        <v>1.876</v>
       </c>
       <c r="I6" t="n">
-        <v>1.6141</v>
+        <v>1.2214</v>
       </c>
       <c r="J6" t="n">
-        <v>2.472</v>
+        <v>1.8527</v>
       </c>
       <c r="K6" t="n">
-        <v>1.6458</v>
+        <v>1.7049</v>
       </c>
       <c r="L6" t="n">
-        <v>0.8262</v>
+        <v>0.1478</v>
       </c>
       <c r="M6" t="n">
-        <v>0.8161</v>
+        <v>1.2448</v>
       </c>
       <c r="N6" t="n">
-        <v>0.0283</v>
+        <v>0.1711</v>
       </c>
       <c r="O6" t="n">
-        <v>0.7879</v>
+        <v>1.0736</v>
       </c>
       <c r="P6" t="n">
-        <v>1.4568</v>
+        <v>-2.7055</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-4.1624</v>
       </c>
       <c r="R6" t="n">
         <v>1.4568</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.5338</v>
+        <v>1.7676</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.7705</v>
+        <v>1.6102</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.7633</v>
+        <v>0.1573</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.3538</v>
+        <v>-1.1675</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.3538</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-1.1675</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>D. RAMÍREZ SÁNCHEZ</t>
+          <t>J. LUIS</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>2.0668</v>
+        <v>0.9764</v>
       </c>
       <c r="E7" t="n">
-        <v>0.1777</v>
+        <v>1.427</v>
       </c>
       <c r="F7" t="n">
-        <v>1.8891</v>
+        <v>-0.4505</v>
       </c>
       <c r="G7" t="n">
-        <v>0.9399999999999999</v>
+        <v>1.2524</v>
       </c>
       <c r="H7" t="n">
-        <v>0.5482</v>
+        <v>-0.6654</v>
       </c>
       <c r="I7" t="n">
-        <v>0.3919</v>
+        <v>1.9178</v>
       </c>
       <c r="J7" t="n">
-        <v>0.8177</v>
+        <v>2.6324</v>
       </c>
       <c r="K7" t="n">
-        <v>0.7483</v>
+        <v>0.6820000000000001</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0694</v>
+        <v>1.9504</v>
       </c>
       <c r="M7" t="n">
-        <v>0.1223</v>
+        <v>-1.38</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.2002</v>
+        <v>-1.3473</v>
       </c>
       <c r="O7" t="n">
-        <v>0.3225</v>
+        <v>-0.0326</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>-1.0406</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.0406</v>
+        <v>-2.0812</v>
       </c>
       <c r="R7" t="n">
         <v>1.0406</v>
       </c>
       <c r="S7" t="n">
-        <v>1.1267</v>
+        <v>1.2246</v>
       </c>
       <c r="T7" t="n">
-        <v>0.4005</v>
+        <v>0.6458</v>
       </c>
       <c r="U7" t="n">
-        <v>0.7262</v>
+        <v>0.5787</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>-0.4599</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>0.23</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-0.6899</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.4072</v>
+        <v>0.5065</v>
       </c>
       <c r="E8" t="n">
-        <v>0.6199</v>
+        <v>1.3281</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.0271</v>
+        <v>-0.8216</v>
       </c>
       <c r="G8" t="n">
         <v>-0.5001</v>
@@ -1078,13 +1078,13 @@
         <v>0.4162</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.0341</v>
+        <v>-0.1204</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.64</v>
+        <v>0.06809999999999999</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.394</v>
+        <v>-0.1885</v>
       </c>
       <c r="V8" t="n">
         <v>1.7513</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.0212</v>
+        <v>-0.2836</v>
       </c>
       <c r="E9" t="n">
-        <v>0.3129</v>
+        <v>1.0211</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.3341</v>
+        <v>-1.3047</v>
       </c>
       <c r="G9" t="n">
         <v>2.4503</v>
@@ -1156,13 +1156,13 @@
         <v>0.4162</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.4091</v>
+        <v>0.3285</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.5748</v>
+        <v>0.1334</v>
       </c>
       <c r="U9" t="n">
-        <v>0.1657</v>
+        <v>0.1951</v>
       </c>
       <c r="V9" t="n">
         <v>-1.3975</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.5337</v>
+        <v>-0.6704</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.2246</v>
+        <v>-1.743</v>
       </c>
       <c r="F10" t="n">
-        <v>0.6909</v>
+        <v>1.0725</v>
       </c>
       <c r="G10" t="n">
         <v>1.8836</v>
@@ -1234,13 +1234,13 @@
         <v>1.4568</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.7086</v>
+        <v>0.1546</v>
       </c>
       <c r="T10" t="n">
-        <v>-1.0315</v>
+        <v>0.4501</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.6771</v>
+        <v>-0.2955</v>
       </c>
       <c r="V10" t="n">
         <v>-1.0437</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.7095</v>
+        <v>-2.4555</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.2163</v>
+        <v>-0.1092</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.4931</v>
+        <v>-2.3463</v>
       </c>
       <c r="G11" t="n">
         <v>-0.8537</v>
@@ -1312,13 +1312,13 @@
         <v>0.2081</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.4365</v>
+        <v>-0.1825</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.3915</v>
+        <v>-0.2843</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.045</v>
+        <v>0.1018</v>
       </c>
       <c r="V11" t="n">
         <v>-1.6275</v>
@@ -1345,10 +1345,10 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.7702</v>
+        <v>-2.5559</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.6595</v>
+        <v>-2.4452</v>
       </c>
       <c r="F12" t="n">
         <v>-0.1107</v>
@@ -1390,10 +1390,10 @@
         <v>0.2081</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.2081</v>
+        <v>0.0062</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.2486</v>
+        <v>-0.0343</v>
       </c>
       <c r="U12" t="n">
         <v>0.0405</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>10.6463</v>
+        <v>11.6249</v>
       </c>
       <c r="E13" t="n">
-        <v>7.7227</v>
+        <v>8.7012</v>
       </c>
       <c r="F13" t="n">
-        <v>2.9237</v>
+        <v>2.9236</v>
       </c>
       <c r="G13" t="n">
         <v>19.2064</v>
@@ -1459,7 +1459,7 @@
         <v>5.2049</v>
       </c>
       <c r="P13" t="n">
-        <v>-7.2841</v>
+        <v>-7.284099999999999</v>
       </c>
       <c r="Q13" t="n">
         <v>-16.6496</v>
@@ -1468,13 +1468,13 @@
         <v>9.3652</v>
       </c>
       <c r="S13" t="n">
-        <v>3.7121</v>
+        <v>4.691</v>
       </c>
       <c r="T13" t="n">
-        <v>3.2746</v>
+        <v>4.2531</v>
       </c>
       <c r="U13" t="n">
-        <v>0.4377999999999999</v>
+        <v>0.4376999999999999</v>
       </c>
       <c r="V13" t="n">
         <v>-4.9885</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>4.5216</v>
+        <v>5.2502</v>
       </c>
       <c r="E14" t="n">
-        <v>4.8161</v>
+        <v>5.1375</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.2944</v>
+        <v>0.1127</v>
       </c>
       <c r="G14" t="n">
         <v>0.9855</v>
@@ -1546,13 +1546,13 @@
         <v>1.8731</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.672</v>
+        <v>0.0566</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.1743</v>
+        <v>0.1472</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.4978</v>
+        <v>-0.0906</v>
       </c>
       <c r="V14" t="n">
         <v>2.3351</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.829</v>
+        <v>1.9528</v>
       </c>
       <c r="E15" t="n">
-        <v>1.9956</v>
+        <v>1.8884</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.1665</v>
+        <v>0.0644</v>
       </c>
       <c r="G15" t="n">
         <v>-1.3539</v>
@@ -1624,13 +1624,13 @@
         <v>1.0406</v>
       </c>
       <c r="S15" t="n">
-        <v>0.1611</v>
+        <v>0.2849</v>
       </c>
       <c r="T15" t="n">
-        <v>0.2048</v>
+        <v>0.0977</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.0437</v>
+        <v>0.1873</v>
       </c>
       <c r="V15" t="n">
         <v>1.9813</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.4614</v>
+        <v>0.5955</v>
       </c>
       <c r="E16" t="n">
-        <v>0.6318</v>
+        <v>0.4175</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.1703</v>
+        <v>0.1781</v>
       </c>
       <c r="G16" t="n">
         <v>-0.2471</v>
@@ -1702,13 +1702,13 @@
         <v>1.2487</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.5402</v>
+        <v>-0.4061</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.1338</v>
+        <v>-0.3481</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.4064</v>
+        <v>-0.058</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>J. SANTA BARBARA CARCELEN</t>
+          <t>J. BALDERAS MARTÍN</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.0559</v>
+        <v>0.0303</v>
       </c>
       <c r="E17" t="n">
-        <v>1.135</v>
+        <v>-0.1776</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.1909</v>
+        <v>0.2079</v>
       </c>
       <c r="G17" t="n">
-        <v>-3.3585</v>
+        <v>0.2155</v>
       </c>
       <c r="H17" t="n">
-        <v>1.8527</v>
+        <v>-0.2131</v>
       </c>
       <c r="I17" t="n">
-        <v>-5.2112</v>
+        <v>0.4286</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.9173</v>
+        <v>0.07679999999999999</v>
       </c>
       <c r="K17" t="n">
-        <v>1.91</v>
+        <v>0.07679999999999999</v>
       </c>
       <c r="L17" t="n">
-        <v>-2.8273</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>-2.4412</v>
+        <v>0.1387</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.0573</v>
+        <v>-0.2899</v>
       </c>
       <c r="O17" t="n">
-        <v>-2.3839</v>
+        <v>0.4286</v>
       </c>
       <c r="P17" t="n">
-        <v>1.2487</v>
+        <v>0.2081</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.0406</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>2.2893</v>
+        <v>0.2081</v>
       </c>
       <c r="S17" t="n">
-        <v>1.2402</v>
+        <v>-0.2694</v>
       </c>
       <c r="T17" t="n">
-        <v>1.1116</v>
+        <v>-0.1305</v>
       </c>
       <c r="U17" t="n">
-        <v>0.1286</v>
+        <v>-0.139</v>
       </c>
       <c r="V17" t="n">
-        <v>0.8137</v>
+        <v>-0.1238</v>
       </c>
       <c r="W17" t="n">
-        <v>1.9813</v>
+        <v>-0.1238</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.1675</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>J. BALDERAS MARTÍN</t>
+          <t>J. MORENO POZA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,64 +1813,64 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.0578</v>
+        <v>-0.5363</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.1776</v>
+        <v>-1.0661</v>
       </c>
       <c r="F18" t="n">
-        <v>0.1198</v>
+        <v>0.5299</v>
       </c>
       <c r="G18" t="n">
-        <v>0.2155</v>
+        <v>-0.5004999999999999</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.2131</v>
+        <v>-0.5095</v>
       </c>
       <c r="I18" t="n">
-        <v>0.4286</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="J18" t="n">
-        <v>0.07679999999999999</v>
+        <v>0.1935</v>
       </c>
       <c r="K18" t="n">
-        <v>0.07679999999999999</v>
+        <v>0.1151</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>0.0784</v>
       </c>
       <c r="M18" t="n">
-        <v>0.1387</v>
+        <v>-0.694</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.2899</v>
+        <v>-0.6247</v>
       </c>
       <c r="O18" t="n">
-        <v>0.4286</v>
+        <v>-0.0694</v>
       </c>
       <c r="P18" t="n">
-        <v>0.2081</v>
+        <v>-0.2081</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-1.0406</v>
       </c>
       <c r="R18" t="n">
-        <v>0.2081</v>
+        <v>0.8325</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.3575</v>
+        <v>0.1724</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.1305</v>
+        <v>-0.2191</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.227</v>
+        <v>0.3915</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.1238</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>-0.1238</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
         <v>0</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.0615</v>
+        <v>-0.6115</v>
       </c>
       <c r="E19" t="n">
-        <v>0.9647</v>
+        <v>0.5361</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.0262</v>
+        <v>-1.1475</v>
       </c>
       <c r="G19" t="n">
         <v>0.4308</v>
@@ -1936,13 +1936,13 @@
         <v>1.2487</v>
       </c>
       <c r="S19" t="n">
-        <v>0.0072</v>
+        <v>-0.5427999999999999</v>
       </c>
       <c r="T19" t="n">
-        <v>0.4625</v>
+        <v>0.0339</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.4553</v>
+        <v>-0.5767</v>
       </c>
       <c r="V19" t="n">
         <v>-0.7076</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>J. MORENO POZA</t>
+          <t>J. SANTA BARBARA CARCELEN</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.6434</v>
+        <v>-0.6773</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.1733</v>
+        <v>0.4921</v>
       </c>
       <c r="F20" t="n">
-        <v>0.5299</v>
+        <v>-1.1694</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.5004999999999999</v>
+        <v>-3.3585</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.5095</v>
+        <v>1.8527</v>
       </c>
       <c r="I20" t="n">
-        <v>0.008999999999999999</v>
+        <v>-5.2112</v>
       </c>
       <c r="J20" t="n">
-        <v>0.1935</v>
+        <v>-0.9173</v>
       </c>
       <c r="K20" t="n">
-        <v>0.1151</v>
+        <v>1.91</v>
       </c>
       <c r="L20" t="n">
-        <v>0.0784</v>
+        <v>-2.8273</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.694</v>
+        <v>-2.4412</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.6247</v>
+        <v>-0.0573</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.0694</v>
+        <v>-2.3839</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.2081</v>
+        <v>1.2487</v>
       </c>
       <c r="Q20" t="n">
         <v>-1.0406</v>
       </c>
       <c r="R20" t="n">
-        <v>0.8325</v>
+        <v>2.2893</v>
       </c>
       <c r="S20" t="n">
-        <v>0.06519999999999999</v>
+        <v>0.6188</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.3262</v>
+        <v>0.4687</v>
       </c>
       <c r="U20" t="n">
-        <v>0.3915</v>
+        <v>0.1501</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>0.8137</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.9813</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>-1.1675</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.5023</v>
+        <v>-0.8339</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.1483</v>
+        <v>-0.5054</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.354</v>
+        <v>-0.3286</v>
       </c>
       <c r="G21" t="n">
         <v>-0.8277</v>
@@ -2092,13 +2092,13 @@
         <v>1.6649</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.2989</v>
+        <v>-0.6304999999999999</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.9663</v>
+        <v>-0.3233</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.3327</v>
+        <v>-0.3072</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>K. FELIZOR</t>
+          <t>A. LOPES MARQUES</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,64 +2125,64 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.9018</v>
+        <v>-2.61</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.2718</v>
+        <v>-2.4457</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.6301</v>
+        <v>-0.1644</v>
       </c>
       <c r="G22" t="n">
-        <v>-2.2967</v>
+        <v>-4.1993</v>
       </c>
       <c r="H22" t="n">
-        <v>-1.13</v>
+        <v>-0.8593</v>
       </c>
       <c r="I22" t="n">
-        <v>-1.1667</v>
+        <v>-3.34</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.3083</v>
+        <v>-2.644</v>
       </c>
       <c r="K22" t="n">
-        <v>1.0421</v>
+        <v>-1.3328</v>
       </c>
       <c r="L22" t="n">
-        <v>-1.3504</v>
+        <v>-1.3112</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.9884</v>
+        <v>-1.5553</v>
       </c>
       <c r="N22" t="n">
-        <v>-2.1722</v>
+        <v>0.4735</v>
       </c>
       <c r="O22" t="n">
-        <v>0.1837</v>
+        <v>-2.0288</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.8325</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>-3.1218</v>
+        <v>-1.0406</v>
       </c>
       <c r="R22" t="n">
-        <v>2.2893</v>
+        <v>1.0406</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.0026</v>
+        <v>0.1918</v>
       </c>
       <c r="T22" t="n">
-        <v>0.9283</v>
+        <v>-0.1586</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.9308999999999999</v>
+        <v>0.3504</v>
       </c>
       <c r="V22" t="n">
-        <v>0.23</v>
+        <v>1.3975</v>
       </c>
       <c r="W22" t="n">
-        <v>0.23</v>
+        <v>1.3975</v>
       </c>
       <c r="X22" t="n">
         <v>0</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.9687</v>
+        <v>-2.8116</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.6499</v>
+        <v>-1.7571</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.3188</v>
+        <v>-1.0545</v>
       </c>
       <c r="G23" t="n">
         <v>-3.0893</v>
@@ -2248,13 +2248,13 @@
         <v>1.2487</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.1905</v>
+        <v>-0.0334</v>
       </c>
       <c r="T23" t="n">
-        <v>0.2172</v>
+        <v>0.11</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.4077</v>
+        <v>-0.1435</v>
       </c>
       <c r="V23" t="n">
         <v>-0.9376</v>
@@ -2269,7 +2269,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A. LOPES MARQUES</t>
+          <t>K. FELIZOR</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,64 +2281,64 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-2.976</v>
+        <v>-3.3916</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.8743</v>
+        <v>-3.0219</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.1017</v>
+        <v>-0.3697</v>
       </c>
       <c r="G24" t="n">
-        <v>-4.1993</v>
+        <v>-2.2967</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.8593</v>
+        <v>-1.13</v>
       </c>
       <c r="I24" t="n">
-        <v>-3.34</v>
+        <v>-1.1667</v>
       </c>
       <c r="J24" t="n">
-        <v>-2.644</v>
+        <v>-0.3083</v>
       </c>
       <c r="K24" t="n">
-        <v>-1.3328</v>
+        <v>1.0421</v>
       </c>
       <c r="L24" t="n">
-        <v>-1.3112</v>
+        <v>-1.3504</v>
       </c>
       <c r="M24" t="n">
-        <v>-1.5553</v>
+        <v>-1.9884</v>
       </c>
       <c r="N24" t="n">
-        <v>0.4735</v>
+        <v>-2.1722</v>
       </c>
       <c r="O24" t="n">
-        <v>-2.0288</v>
+        <v>0.1837</v>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>-0.8325</v>
       </c>
       <c r="Q24" t="n">
-        <v>-1.0406</v>
+        <v>-3.1218</v>
       </c>
       <c r="R24" t="n">
-        <v>1.0406</v>
+        <v>2.2893</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.1742</v>
+        <v>-0.4924</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.5872000000000001</v>
+        <v>0.1782</v>
       </c>
       <c r="U24" t="n">
-        <v>0.413</v>
+        <v>-0.6706</v>
       </c>
       <c r="V24" t="n">
-        <v>1.3975</v>
+        <v>0.23</v>
       </c>
       <c r="W24" t="n">
-        <v>1.3975</v>
+        <v>0.23</v>
       </c>
       <c r="X24" t="n">
         <v>0</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-6.2909</v>
+        <v>-5.5741</v>
       </c>
       <c r="E25" t="n">
-        <v>-3.1714</v>
+        <v>-2.4213</v>
       </c>
       <c r="F25" t="n">
-        <v>-3.1195</v>
+        <v>-3.1528</v>
       </c>
       <c r="G25" t="n">
         <v>-4.9652</v>
@@ -2404,13 +2404,13 @@
         <v>1.6649</v>
       </c>
       <c r="S25" t="n">
-        <v>-1.95</v>
+        <v>-1.2332</v>
       </c>
       <c r="T25" t="n">
-        <v>-1.0439</v>
+        <v>-0.2938</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.9061</v>
+        <v>-0.9394</v>
       </c>
       <c r="V25" t="n">
         <v>0</v>
@@ -2437,19 +2437,19 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-10.6463</v>
+        <v>-9.217499999999999</v>
       </c>
       <c r="E26" t="n">
-        <v>-2.923399999999999</v>
+        <v>-2.923500000000001</v>
       </c>
       <c r="F26" t="n">
-        <v>-7.7227</v>
+        <v>-6.2939</v>
       </c>
       <c r="G26" t="n">
         <v>-19.2064</v>
       </c>
       <c r="H26" t="n">
-        <v>-4.776200000000001</v>
+        <v>-4.7762</v>
       </c>
       <c r="I26" t="n">
         <v>-14.4303</v>
@@ -2467,13 +2467,13 @@
         <v>-17.7186</v>
       </c>
       <c r="N26" t="n">
-        <v>-8.493500000000001</v>
+        <v>-8.493499999999999</v>
       </c>
       <c r="O26" t="n">
-        <v>-9.225500000000002</v>
+        <v>-9.2255</v>
       </c>
       <c r="P26" t="n">
-        <v>7.284199999999998</v>
+        <v>7.2842</v>
       </c>
       <c r="Q26" t="n">
         <v>-9.365399999999999</v>
@@ -2482,13 +2482,13 @@
         <v>16.6494</v>
       </c>
       <c r="S26" t="n">
-        <v>-3.7122</v>
+        <v>-2.2833</v>
       </c>
       <c r="T26" t="n">
-        <v>-0.4378000000000001</v>
+        <v>-0.4377</v>
       </c>
       <c r="U26" t="n">
-        <v>-3.2745</v>
+        <v>-1.8457</v>
       </c>
       <c r="V26" t="n">
         <v>4.9886</v>
